--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table115.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table115.xlsx
@@ -61,8 +61,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -101,7 +101,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,12 +237,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -290,11 +284,11 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="23">
     <cellStyle name="Accent1 - 20%" xfId="1"/>
@@ -636,7 +630,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -2111,12 +2105,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <Used_x0020_in_x0020_Chapter xmlns="d1607db4-bd3f-4f82-a312-bf7e283d0a6b">true</Used_x0020_in_x0020_Chapter>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2180,15 +2173,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <Used_x0020_in_x0020_Chapter xmlns="d1607db4-bd3f-4f82-a312-bf7e283d0a6b">true</Used_x0020_in_x0020_Chapter>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66F5C317-175E-4CCC-8537-9A5743AC32DE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B94ECBCA-4630-4771-B032-AA90D0E5FE69}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
@@ -2200,7 +2194,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B94ECBCA-4630-4771-B032-AA90D0E5FE69}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66F5C317-175E-4CCC-8537-9A5743AC32DE}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>